--- a/DateBase/orders/Dang Nguyen48_2026-4-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-24.xlsx
@@ -967,6 +967,9 @@
       <c r="G2" t="str">
         <v>01010105109551010105555555551520555510101510105555515555101020151010510106655510</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
